--- a/Analyse_frequence.xlsx
+++ b/Analyse_frequence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\Desktop\Wendeka Risk\portofolio\exemple_tarification_IARD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C78021-B2E6-44AE-A39E-7BC242884B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9A4AE0-85E5-43E7-8F87-4FBED37CB922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19470" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1196,6 +1196,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="315246480"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1986,6 +1987,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="298748160"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -2216,10 +2218,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.74398049634027053</c:v>
+                  <c:v>2.0898827591632378</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.34089257346433199</c:v>
+                  <c:v>2.1727474312327715</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2277,6 +2279,23 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>exterior_cladding!$B$53:$B$55</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Brick</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Wood</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Vinyl</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>exterior_cladding!$H$53:$H$55</c:f>
@@ -2334,6 +2353,23 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>exterior_cladding!$B$53:$B$55</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Brick</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Wood</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Vinyl</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>exterior_cladding!$G$53:$G$55</c:f>
@@ -2391,6 +2427,23 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>exterior_cladding!$B$53:$B$55</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Brick</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Wood</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Vinyl</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>exterior_cladding!$F$53:$F$55</c:f>
@@ -2588,6 +2641,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="406494735"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -4741,7 +4795,7 @@
         <v>Vinyl</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:L10" si="1">SUMIFS($D:$D,$C:$C,I$4,$B:$B,$H6)</f>
+        <f t="shared" ref="I6:L7" si="1">SUMIFS($D:$D,$C:$C,I$4,$B:$B,$H6)</f>
         <v>749.00585260054095</v>
       </c>
       <c r="J6">
@@ -4757,7 +4811,7 @@
         <v>4424.3054589084304</v>
       </c>
       <c r="M6">
-        <f t="shared" ref="M6:M10" si="2">SUM(I6:L6)</f>
+        <f t="shared" ref="M6:M7" si="2">SUM(I6:L6)</f>
         <v>10525.844564581901</v>
       </c>
     </row>
@@ -5622,7 +5676,7 @@
         <v>2.4450877720713602</v>
       </c>
       <c r="I53" s="1">
-        <f>C53/$C$56</f>
+        <f>F53/$F$53</f>
         <v>1</v>
       </c>
     </row>
@@ -5652,8 +5706,8 @@
         <v>5.1103738556443403</v>
       </c>
       <c r="I54" s="1">
-        <f>C54/$C$56</f>
-        <v>0.74398049634027053</v>
+        <f t="shared" ref="I54:I55" si="5">F54/$F$53</f>
+        <v>2.0898827591632378</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.45">
@@ -5682,8 +5736,8 @@
         <v>5.3144527597915197</v>
       </c>
       <c r="I55" s="1">
-        <f>C55/$C$56</f>
-        <v>0.34089257346433199</v>
+        <f t="shared" si="5"/>
+        <v>2.1727474312327715</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.45">
